--- a/E/PCE06D.xlsx
+++ b/E/PCE06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4260" uniqueCount="1484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4260" uniqueCount="1483">
   <si>
     <t/>
   </si>
@@ -2108,9 +2108,6 @@
   </si>
   <si>
     <t>VSL G-H FLWS BRGT180</t>
-  </si>
-  <si>
-    <t>TG,(E-27H)</t>
   </si>
   <si>
     <t>20021816</t>
@@ -11483,15 +11480,15 @@
         <v>12</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>699</v>
+        <v>533</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="B332" s="1" t="s">
         <v>700</v>
-      </c>
-      <c r="B332" s="1" t="s">
-        <v>701</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>3</v>
@@ -11508,10 +11505,10 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="B333" s="1" t="s">
         <v>702</v>
-      </c>
-      <c r="B333" s="1" t="s">
-        <v>703</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>3</v>
@@ -11528,10 +11525,10 @@
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B334" s="1" t="s">
         <v>704</v>
-      </c>
-      <c r="B334" s="1" t="s">
-        <v>705</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>3</v>
@@ -11548,10 +11545,10 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B335" s="1" t="s">
         <v>706</v>
-      </c>
-      <c r="B335" s="1" t="s">
-        <v>707</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>3</v>
@@ -11568,10 +11565,10 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="B336" s="1" t="s">
         <v>708</v>
-      </c>
-      <c r="B336" s="1" t="s">
-        <v>709</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>3</v>
@@ -11588,10 +11585,10 @@
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="B337" s="1" t="s">
         <v>710</v>
-      </c>
-      <c r="B337" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>3</v>
@@ -11608,10 +11605,10 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="B338" s="1" t="s">
         <v>712</v>
-      </c>
-      <c r="B338" s="1" t="s">
-        <v>713</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>3</v>
@@ -11628,10 +11625,10 @@
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="B339" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="B339" s="1" t="s">
-        <v>715</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>3</v>
@@ -11648,10 +11645,10 @@
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B340" s="1" t="s">
         <v>716</v>
-      </c>
-      <c r="B340" s="1" t="s">
-        <v>717</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>3</v>
@@ -11668,16 +11665,16 @@
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="B341" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="B341" s="1" t="s">
+      <c r="C341" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D341" s="1" t="s">
         <v>719</v>
-      </c>
-      <c r="C341" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D341" s="1" t="s">
-        <v>720</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>4</v>
@@ -11688,16 +11685,16 @@
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="B342" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="B342" s="1" t="s">
-        <v>722</v>
-      </c>
       <c r="C342" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>8</v>
@@ -11708,16 +11705,16 @@
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B343" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="B343" s="1" t="s">
-        <v>724</v>
-      </c>
       <c r="C343" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E343" s="1" t="s">
         <v>12</v>
@@ -11728,16 +11725,16 @@
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="B344" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="B344" s="1" t="s">
-        <v>726</v>
-      </c>
       <c r="C344" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>15</v>
@@ -11748,16 +11745,16 @@
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="B345" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="B345" s="1" t="s">
-        <v>728</v>
-      </c>
       <c r="C345" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>18</v>
@@ -11768,16 +11765,16 @@
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="B346" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="B346" s="1" t="s">
-        <v>730</v>
-      </c>
       <c r="C346" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E346" s="1" t="s">
         <v>21</v>
@@ -11788,16 +11785,16 @@
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="B347" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="B347" s="1" t="s">
-        <v>732</v>
-      </c>
       <c r="C347" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>24</v>
@@ -11808,16 +11805,16 @@
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="B348" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="B348" s="1" t="s">
-        <v>734</v>
-      </c>
       <c r="C348" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>55</v>
@@ -11828,16 +11825,16 @@
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="B349" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="B349" s="1" t="s">
-        <v>736</v>
-      </c>
       <c r="C349" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>28</v>
@@ -11848,16 +11845,16 @@
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="B350" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="B350" s="1" t="s">
-        <v>738</v>
-      </c>
       <c r="C350" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>31</v>
@@ -11868,16 +11865,16 @@
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="B351" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="B351" s="1" t="s">
-        <v>740</v>
-      </c>
       <c r="C351" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>34</v>
@@ -11888,16 +11885,16 @@
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="B352" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="B352" s="1" t="s">
-        <v>742</v>
-      </c>
       <c r="C352" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E352" s="1" t="s">
         <v>37</v>
@@ -11908,16 +11905,16 @@
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="B353" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="B353" s="1" t="s">
-        <v>744</v>
-      </c>
       <c r="C353" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>66</v>
@@ -11928,16 +11925,16 @@
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="B354" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="B354" s="1" t="s">
-        <v>746</v>
-      </c>
       <c r="C354" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>98</v>
@@ -11948,16 +11945,16 @@
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="B355" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="B355" s="1" t="s">
+      <c r="C355" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D355" s="1" t="s">
         <v>748</v>
-      </c>
-      <c r="C355" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D355" s="1" t="s">
-        <v>749</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>4</v>
@@ -11968,16 +11965,16 @@
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B356" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="B356" s="1" t="s">
-        <v>751</v>
-      </c>
       <c r="C356" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E356" s="1" t="s">
         <v>8</v>
@@ -11988,16 +11985,16 @@
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B357" s="1" t="s">
         <v>752</v>
       </c>
-      <c r="B357" s="1" t="s">
-        <v>753</v>
-      </c>
       <c r="C357" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E357" s="1" t="s">
         <v>12</v>
@@ -12008,16 +12005,16 @@
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="B358" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="B358" s="1" t="s">
-        <v>755</v>
-      </c>
       <c r="C358" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>15</v>
@@ -12028,16 +12025,16 @@
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="B359" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="B359" s="1" t="s">
-        <v>757</v>
-      </c>
       <c r="C359" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>18</v>
@@ -12048,16 +12045,16 @@
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B360" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="B360" s="1" t="s">
-        <v>759</v>
-      </c>
       <c r="C360" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>21</v>
@@ -12068,16 +12065,16 @@
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="B361" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="B361" s="1" t="s">
-        <v>761</v>
-      </c>
       <c r="C361" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>24</v>
@@ -12088,16 +12085,16 @@
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="B362" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="B362" s="1" t="s">
-        <v>763</v>
-      </c>
       <c r="C362" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>55</v>
@@ -12108,16 +12105,16 @@
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="B363" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="B363" s="1" t="s">
-        <v>765</v>
-      </c>
       <c r="C363" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>28</v>
@@ -12128,16 +12125,16 @@
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="B364" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="B364" s="1" t="s">
-        <v>767</v>
-      </c>
       <c r="C364" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>31</v>
@@ -12148,16 +12145,16 @@
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="B365" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="B365" s="1" t="s">
-        <v>769</v>
-      </c>
       <c r="C365" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>34</v>
@@ -12168,16 +12165,16 @@
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B366" s="1" t="s">
         <v>770</v>
       </c>
-      <c r="B366" s="1" t="s">
-        <v>771</v>
-      </c>
       <c r="C366" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D366" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>37</v>
@@ -12188,16 +12185,16 @@
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="B367" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="B367" s="1" t="s">
-        <v>773</v>
-      </c>
       <c r="C367" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>66</v>
@@ -12208,16 +12205,16 @@
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="B368" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="B368" s="1" t="s">
-        <v>775</v>
-      </c>
       <c r="C368" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>98</v>
@@ -12228,16 +12225,16 @@
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="B369" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="B369" s="1" t="s">
-        <v>777</v>
-      </c>
       <c r="C369" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D369" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E369" s="1" t="s">
         <v>101</v>
@@ -12248,16 +12245,16 @@
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="B370" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="B370" s="1" t="s">
-        <v>779</v>
-      </c>
       <c r="C370" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D370" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E370" s="1" t="s">
         <v>104</v>
@@ -12268,16 +12265,16 @@
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="B371" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="B371" s="1" t="s">
-        <v>781</v>
-      </c>
       <c r="C371" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>107</v>
@@ -12288,16 +12285,16 @@
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="B372" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="B372" s="1" t="s">
-        <v>783</v>
-      </c>
       <c r="C372" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D372" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E372" s="1" t="s">
         <v>110</v>
@@ -12308,16 +12305,16 @@
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="B373" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="B373" s="1" t="s">
-        <v>785</v>
-      </c>
       <c r="C373" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D373" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E373" s="1" t="s">
         <v>150</v>
@@ -12328,16 +12325,16 @@
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="B374" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="B374" s="1" t="s">
+      <c r="C374" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D374" s="1" t="s">
         <v>787</v>
-      </c>
-      <c r="C374" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D374" s="1" t="s">
-        <v>788</v>
       </c>
       <c r="E374" s="1" t="s">
         <v>4</v>
@@ -12348,16 +12345,16 @@
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="B375" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="B375" s="1" t="s">
-        <v>790</v>
-      </c>
       <c r="C375" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E375" s="1" t="s">
         <v>8</v>
@@ -12368,16 +12365,16 @@
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="B376" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="B376" s="1" t="s">
-        <v>792</v>
-      </c>
       <c r="C376" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D376" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E376" s="1" t="s">
         <v>12</v>
@@ -12388,16 +12385,16 @@
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="B377" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="B377" s="1" t="s">
-        <v>794</v>
-      </c>
       <c r="C377" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D377" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E377" s="1" t="s">
         <v>15</v>
@@ -12408,16 +12405,16 @@
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="B378" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="B378" s="1" t="s">
-        <v>796</v>
-      </c>
       <c r="C378" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D378" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E378" s="1" t="s">
         <v>18</v>
@@ -12428,16 +12425,16 @@
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="B379" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="B379" s="1" t="s">
-        <v>798</v>
-      </c>
       <c r="C379" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>21</v>
@@ -12448,16 +12445,16 @@
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="B380" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="B380" s="1" t="s">
-        <v>800</v>
-      </c>
       <c r="C380" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D380" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E380" s="1" t="s">
         <v>24</v>
@@ -12468,16 +12465,16 @@
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="B381" s="1" t="s">
         <v>801</v>
       </c>
-      <c r="B381" s="1" t="s">
-        <v>802</v>
-      </c>
       <c r="C381" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>55</v>
@@ -12488,16 +12485,16 @@
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="B382" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="B382" s="1" t="s">
-        <v>804</v>
-      </c>
       <c r="C382" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E382" s="1" t="s">
         <v>28</v>
@@ -12508,16 +12505,16 @@
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="B383" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="B383" s="1" t="s">
-        <v>806</v>
-      </c>
       <c r="C383" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E383" s="1" t="s">
         <v>31</v>
@@ -12528,16 +12525,16 @@
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="B384" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="B384" s="1" t="s">
-        <v>808</v>
-      </c>
       <c r="C384" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E384" s="1" t="s">
         <v>34</v>
@@ -12548,16 +12545,16 @@
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="B385" s="1" t="s">
         <v>809</v>
       </c>
-      <c r="B385" s="1" t="s">
-        <v>810</v>
-      </c>
       <c r="C385" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E385" s="1" t="s">
         <v>37</v>
@@ -12568,16 +12565,16 @@
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="B386" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="B386" s="1" t="s">
-        <v>812</v>
-      </c>
       <c r="C386" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E386" s="1" t="s">
         <v>66</v>
@@ -12588,16 +12585,16 @@
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="B387" s="1" t="s">
         <v>813</v>
       </c>
-      <c r="B387" s="1" t="s">
-        <v>814</v>
-      </c>
       <c r="C387" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E387" s="1" t="s">
         <v>98</v>
@@ -12608,16 +12605,16 @@
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="B388" s="1" t="s">
         <v>815</v>
       </c>
-      <c r="B388" s="1" t="s">
-        <v>816</v>
-      </c>
       <c r="C388" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>101</v>
@@ -12628,16 +12625,16 @@
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="B389" s="1" t="s">
         <v>817</v>
       </c>
-      <c r="B389" s="1" t="s">
-        <v>818</v>
-      </c>
       <c r="C389" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D389" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>104</v>
@@ -12648,16 +12645,16 @@
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="B390" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="B390" s="1" t="s">
-        <v>820</v>
-      </c>
       <c r="C390" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D390" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>107</v>
@@ -12668,16 +12665,16 @@
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="B391" s="1" t="s">
         <v>821</v>
       </c>
-      <c r="B391" s="1" t="s">
-        <v>822</v>
-      </c>
       <c r="C391" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D391" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>110</v>
@@ -12688,16 +12685,16 @@
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="B392" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="B392" s="1" t="s">
-        <v>824</v>
-      </c>
       <c r="C392" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D392" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>150</v>
@@ -12708,16 +12705,16 @@
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="B393" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="B393" s="1" t="s">
-        <v>826</v>
-      </c>
       <c r="C393" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D393" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>153</v>
@@ -12728,16 +12725,16 @@
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="B394" s="1" t="s">
         <v>827</v>
       </c>
-      <c r="B394" s="1" t="s">
+      <c r="C394" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D394" s="1" t="s">
         <v>828</v>
-      </c>
-      <c r="C394" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D394" s="1" t="s">
-        <v>829</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>4</v>
@@ -12748,16 +12745,16 @@
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="B395" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="B395" s="1" t="s">
-        <v>831</v>
-      </c>
       <c r="C395" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D395" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E395" s="1" t="s">
         <v>8</v>
@@ -12768,16 +12765,16 @@
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="B396" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="B396" s="1" t="s">
-        <v>833</v>
-      </c>
       <c r="C396" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D396" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E396" s="1" t="s">
         <v>12</v>
@@ -12788,16 +12785,16 @@
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="B397" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="B397" s="1" t="s">
-        <v>835</v>
-      </c>
       <c r="C397" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D397" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E397" s="1" t="s">
         <v>15</v>
@@ -12808,16 +12805,16 @@
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="B398" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="B398" s="1" t="s">
-        <v>837</v>
-      </c>
       <c r="C398" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D398" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E398" s="1" t="s">
         <v>18</v>
@@ -12828,16 +12825,16 @@
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="B399" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="B399" s="1" t="s">
-        <v>839</v>
-      </c>
       <c r="C399" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D399" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E399" s="1" t="s">
         <v>21</v>
@@ -12848,16 +12845,16 @@
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="B400" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="B400" s="1" t="s">
-        <v>841</v>
-      </c>
       <c r="C400" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D400" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E400" s="1" t="s">
         <v>24</v>
@@ -12868,16 +12865,16 @@
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="B401" s="1" t="s">
         <v>842</v>
       </c>
-      <c r="B401" s="1" t="s">
-        <v>843</v>
-      </c>
       <c r="C401" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D401" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E401" s="1" t="s">
         <v>55</v>
@@ -12888,16 +12885,16 @@
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="B402" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="B402" s="1" t="s">
-        <v>845</v>
-      </c>
       <c r="C402" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D402" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E402" s="1" t="s">
         <v>28</v>
@@ -12908,16 +12905,16 @@
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="B403" s="1" t="s">
         <v>846</v>
       </c>
-      <c r="B403" s="1" t="s">
-        <v>847</v>
-      </c>
       <c r="C403" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D403" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E403" s="1" t="s">
         <v>31</v>
@@ -12928,16 +12925,16 @@
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="B404" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="B404" s="1" t="s">
-        <v>849</v>
-      </c>
       <c r="C404" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D404" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E404" s="1" t="s">
         <v>34</v>
@@ -12948,16 +12945,16 @@
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="B405" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="B405" s="1" t="s">
-        <v>851</v>
-      </c>
       <c r="C405" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D405" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>37</v>
@@ -12968,16 +12965,16 @@
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="B406" s="1" t="s">
         <v>852</v>
       </c>
-      <c r="B406" s="1" t="s">
-        <v>853</v>
-      </c>
       <c r="C406" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D406" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>66</v>
@@ -12988,16 +12985,16 @@
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B407" s="1" t="s">
         <v>854</v>
       </c>
-      <c r="B407" s="1" t="s">
-        <v>855</v>
-      </c>
       <c r="C407" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D407" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E407" s="1" t="s">
         <v>98</v>
@@ -13008,16 +13005,16 @@
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="B408" s="1" t="s">
         <v>856</v>
       </c>
-      <c r="B408" s="1" t="s">
-        <v>857</v>
-      </c>
       <c r="C408" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D408" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E408" s="1" t="s">
         <v>101</v>
@@ -13028,16 +13025,16 @@
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="B409" s="1" t="s">
         <v>858</v>
       </c>
-      <c r="B409" s="1" t="s">
-        <v>859</v>
-      </c>
       <c r="C409" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D409" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E409" s="1" t="s">
         <v>104</v>
@@ -13048,16 +13045,16 @@
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="B410" s="1" t="s">
         <v>860</v>
       </c>
-      <c r="B410" s="1" t="s">
-        <v>861</v>
-      </c>
       <c r="C410" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D410" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E410" s="1" t="s">
         <v>107</v>
@@ -13068,16 +13065,16 @@
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="B411" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="B411" s="1" t="s">
-        <v>863</v>
-      </c>
       <c r="C411" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D411" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E411" s="1" t="s">
         <v>110</v>
@@ -13088,16 +13085,16 @@
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="B412" s="1" t="s">
         <v>864</v>
       </c>
-      <c r="B412" s="1" t="s">
-        <v>865</v>
-      </c>
       <c r="C412" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D412" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E412" s="1" t="s">
         <v>150</v>
@@ -13108,16 +13105,16 @@
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="B413" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="B413" s="1" t="s">
-        <v>867</v>
-      </c>
       <c r="C413" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D413" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E413" s="1" t="s">
         <v>153</v>
@@ -13128,16 +13125,16 @@
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="B414" s="1" t="s">
         <v>868</v>
       </c>
-      <c r="B414" s="1" t="s">
-        <v>869</v>
-      </c>
       <c r="C414" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E414" s="1" t="s">
         <v>197</v>
@@ -13148,16 +13145,16 @@
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="B415" s="1" t="s">
         <v>870</v>
       </c>
-      <c r="B415" s="1" t="s">
+      <c r="C415" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D415" s="1" t="s">
         <v>871</v>
-      </c>
-      <c r="C415" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D415" s="1" t="s">
-        <v>872</v>
       </c>
       <c r="E415" s="1" t="s">
         <v>4</v>
@@ -13168,16 +13165,16 @@
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="B416" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="B416" s="1" t="s">
-        <v>874</v>
-      </c>
       <c r="C416" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E416" s="1" t="s">
         <v>8</v>
@@ -13188,16 +13185,16 @@
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="B417" s="1" t="s">
         <v>875</v>
       </c>
-      <c r="B417" s="1" t="s">
-        <v>876</v>
-      </c>
       <c r="C417" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D417" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E417" s="1" t="s">
         <v>12</v>
@@ -13208,16 +13205,16 @@
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="B418" s="1" t="s">
         <v>877</v>
       </c>
-      <c r="B418" s="1" t="s">
-        <v>878</v>
-      </c>
       <c r="C418" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D418" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E418" s="1" t="s">
         <v>15</v>
@@ -13228,16 +13225,16 @@
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="B419" s="1" t="s">
         <v>879</v>
       </c>
-      <c r="B419" s="1" t="s">
-        <v>880</v>
-      </c>
       <c r="C419" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E419" s="1" t="s">
         <v>18</v>
@@ -13248,16 +13245,16 @@
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="B420" s="1" t="s">
         <v>881</v>
       </c>
-      <c r="B420" s="1" t="s">
-        <v>882</v>
-      </c>
       <c r="C420" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D420" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E420" s="1" t="s">
         <v>21</v>
@@ -13268,16 +13265,16 @@
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="B421" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="B421" s="1" t="s">
-        <v>884</v>
-      </c>
       <c r="C421" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D421" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>24</v>
@@ -13288,16 +13285,16 @@
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="B422" s="1" t="s">
         <v>885</v>
       </c>
-      <c r="B422" s="1" t="s">
+      <c r="C422" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D422" s="1" t="s">
         <v>886</v>
-      </c>
-      <c r="C422" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D422" s="1" t="s">
-        <v>887</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>4</v>
@@ -13308,16 +13305,16 @@
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="B423" s="1" t="s">
         <v>888</v>
       </c>
-      <c r="B423" s="1" t="s">
-        <v>889</v>
-      </c>
       <c r="C423" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>8</v>
@@ -13328,16 +13325,16 @@
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="B424" s="1" t="s">
         <v>890</v>
       </c>
-      <c r="B424" s="1" t="s">
-        <v>891</v>
-      </c>
       <c r="C424" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D424" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>12</v>
@@ -13348,36 +13345,36 @@
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="B425" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="B425" s="1" t="s">
-        <v>893</v>
-      </c>
       <c r="C425" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D425" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="B426" s="1" t="s">
         <v>895</v>
       </c>
-      <c r="B426" s="1" t="s">
-        <v>896</v>
-      </c>
       <c r="C426" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D426" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>18</v>
@@ -13388,16 +13385,16 @@
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="B427" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="B427" s="1" t="s">
-        <v>898</v>
-      </c>
       <c r="C427" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D427" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>21</v>
@@ -13408,16 +13405,16 @@
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="B428" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="B428" s="1" t="s">
-        <v>900</v>
-      </c>
       <c r="C428" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E428" s="1" t="s">
         <v>24</v>
@@ -13428,16 +13425,16 @@
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B429" s="1" t="s">
         <v>901</v>
       </c>
-      <c r="B429" s="1" t="s">
-        <v>902</v>
-      </c>
       <c r="C429" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>55</v>
@@ -13448,16 +13445,16 @@
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="B430" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="B430" s="1" t="s">
-        <v>904</v>
-      </c>
       <c r="C430" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D430" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E430" s="1" t="s">
         <v>28</v>
@@ -13468,16 +13465,16 @@
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="B431" s="1" t="s">
         <v>905</v>
       </c>
-      <c r="B431" s="1" t="s">
-        <v>906</v>
-      </c>
       <c r="C431" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D431" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E431" s="1" t="s">
         <v>31</v>
@@ -13488,16 +13485,16 @@
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="B432" s="1" t="s">
         <v>907</v>
       </c>
-      <c r="B432" s="1" t="s">
-        <v>908</v>
-      </c>
       <c r="C432" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D432" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E432" s="1" t="s">
         <v>34</v>
@@ -13508,16 +13505,16 @@
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="B433" s="1" t="s">
         <v>909</v>
       </c>
-      <c r="B433" s="1" t="s">
-        <v>910</v>
-      </c>
       <c r="C433" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D433" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>37</v>
@@ -13528,16 +13525,16 @@
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="B434" s="1" t="s">
         <v>911</v>
       </c>
-      <c r="B434" s="1" t="s">
-        <v>912</v>
-      </c>
       <c r="C434" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D434" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>66</v>
@@ -13548,16 +13545,16 @@
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="B435" s="1" t="s">
         <v>913</v>
       </c>
-      <c r="B435" s="1" t="s">
-        <v>914</v>
-      </c>
       <c r="C435" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>98</v>
@@ -13568,16 +13565,16 @@
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="B436" s="1" t="s">
         <v>915</v>
       </c>
-      <c r="B436" s="1" t="s">
-        <v>916</v>
-      </c>
       <c r="C436" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D436" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>101</v>
@@ -13588,16 +13585,16 @@
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="B437" s="1" t="s">
         <v>917</v>
       </c>
-      <c r="B437" s="1" t="s">
-        <v>918</v>
-      </c>
       <c r="C437" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D437" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>104</v>
@@ -13608,16 +13605,16 @@
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="B438" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="B438" s="1" t="s">
+      <c r="C438" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D438" s="1" t="s">
         <v>920</v>
-      </c>
-      <c r="C438" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D438" s="1" t="s">
-        <v>921</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>4</v>
@@ -13628,16 +13625,16 @@
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="B439" s="1" t="s">
         <v>922</v>
       </c>
-      <c r="B439" s="1" t="s">
-        <v>923</v>
-      </c>
       <c r="C439" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D439" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>8</v>
@@ -13648,16 +13645,16 @@
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="B440" s="1" t="s">
         <v>924</v>
       </c>
-      <c r="B440" s="1" t="s">
-        <v>925</v>
-      </c>
       <c r="C440" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D440" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>12</v>
@@ -13668,16 +13665,16 @@
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="B441" s="1" t="s">
         <v>926</v>
       </c>
-      <c r="B441" s="1" t="s">
-        <v>927</v>
-      </c>
       <c r="C441" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D441" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>15</v>
@@ -13688,16 +13685,16 @@
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="B442" s="1" t="s">
         <v>928</v>
       </c>
-      <c r="B442" s="1" t="s">
-        <v>929</v>
-      </c>
       <c r="C442" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D442" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>18</v>
@@ -13708,16 +13705,16 @@
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="B443" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="B443" s="1" t="s">
-        <v>931</v>
-      </c>
       <c r="C443" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D443" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>21</v>
@@ -13728,16 +13725,16 @@
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="B444" s="1" t="s">
         <v>932</v>
       </c>
-      <c r="B444" s="1" t="s">
-        <v>933</v>
-      </c>
       <c r="C444" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D444" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E444" s="1" t="s">
         <v>24</v>
@@ -13748,16 +13745,16 @@
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="B445" s="1" t="s">
         <v>934</v>
       </c>
-      <c r="B445" s="1" t="s">
-        <v>935</v>
-      </c>
       <c r="C445" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D445" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E445" s="1" t="s">
         <v>55</v>
@@ -13768,16 +13765,16 @@
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="B446" s="1" t="s">
         <v>936</v>
       </c>
-      <c r="B446" s="1" t="s">
-        <v>937</v>
-      </c>
       <c r="C446" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D446" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E446" s="1" t="s">
         <v>28</v>
@@ -13788,16 +13785,16 @@
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="B447" s="1" t="s">
         <v>938</v>
       </c>
-      <c r="B447" s="1" t="s">
-        <v>939</v>
-      </c>
       <c r="C447" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D447" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E447" s="1" t="s">
         <v>31</v>
@@ -13808,16 +13805,16 @@
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="B448" s="1" t="s">
         <v>940</v>
       </c>
-      <c r="B448" s="1" t="s">
-        <v>941</v>
-      </c>
       <c r="C448" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D448" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>34</v>
@@ -13828,16 +13825,16 @@
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="B449" s="1" t="s">
         <v>942</v>
       </c>
-      <c r="B449" s="1" t="s">
-        <v>943</v>
-      </c>
       <c r="C449" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D449" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>37</v>
@@ -13848,16 +13845,16 @@
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="B450" s="1" t="s">
         <v>944</v>
       </c>
-      <c r="B450" s="1" t="s">
-        <v>945</v>
-      </c>
       <c r="C450" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D450" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>66</v>
@@ -13868,16 +13865,16 @@
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="B451" s="1" t="s">
         <v>946</v>
       </c>
-      <c r="B451" s="1" t="s">
-        <v>947</v>
-      </c>
       <c r="C451" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D451" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>98</v>
@@ -13888,16 +13885,16 @@
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="B452" s="1" t="s">
         <v>948</v>
       </c>
-      <c r="B452" s="1" t="s">
-        <v>949</v>
-      </c>
       <c r="C452" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D452" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>101</v>
@@ -13908,16 +13905,16 @@
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="B453" s="1" t="s">
         <v>950</v>
       </c>
-      <c r="B453" s="1" t="s">
+      <c r="C453" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D453" s="1" t="s">
         <v>951</v>
-      </c>
-      <c r="C453" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D453" s="1" t="s">
-        <v>952</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>4</v>
@@ -13928,16 +13925,16 @@
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="B454" s="1" t="s">
         <v>953</v>
       </c>
-      <c r="B454" s="1" t="s">
-        <v>954</v>
-      </c>
       <c r="C454" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D454" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>8</v>
@@ -13948,16 +13945,16 @@
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="B455" s="1" t="s">
         <v>955</v>
       </c>
-      <c r="B455" s="1" t="s">
-        <v>956</v>
-      </c>
       <c r="C455" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D455" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E455" s="1" t="s">
         <v>12</v>
@@ -13968,16 +13965,16 @@
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="B456" s="1" t="s">
         <v>957</v>
       </c>
-      <c r="B456" s="1" t="s">
-        <v>958</v>
-      </c>
       <c r="C456" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D456" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>15</v>
@@ -13988,16 +13985,16 @@
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="B457" s="1" t="s">
         <v>959</v>
       </c>
-      <c r="B457" s="1" t="s">
-        <v>960</v>
-      </c>
       <c r="C457" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D457" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E457" s="1" t="s">
         <v>18</v>
@@ -14008,16 +14005,16 @@
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="B458" s="1" t="s">
         <v>961</v>
       </c>
-      <c r="B458" s="1" t="s">
-        <v>962</v>
-      </c>
       <c r="C458" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D458" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E458" s="1" t="s">
         <v>21</v>
@@ -14028,16 +14025,16 @@
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="B459" s="1" t="s">
         <v>963</v>
       </c>
-      <c r="B459" s="1" t="s">
-        <v>964</v>
-      </c>
       <c r="C459" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D459" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E459" s="1" t="s">
         <v>24</v>
@@ -14048,16 +14045,16 @@
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="B460" s="1" t="s">
         <v>965</v>
       </c>
-      <c r="B460" s="1" t="s">
-        <v>966</v>
-      </c>
       <c r="C460" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D460" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E460" s="1" t="s">
         <v>55</v>
@@ -14068,16 +14065,16 @@
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="B461" s="1" t="s">
         <v>967</v>
       </c>
-      <c r="B461" s="1" t="s">
-        <v>968</v>
-      </c>
       <c r="C461" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D461" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E461" s="1" t="s">
         <v>28</v>
@@ -14088,16 +14085,16 @@
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="B462" s="1" t="s">
         <v>969</v>
       </c>
-      <c r="B462" s="1" t="s">
-        <v>970</v>
-      </c>
       <c r="C462" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D462" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E462" s="1" t="s">
         <v>31</v>
@@ -14108,16 +14105,16 @@
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="B463" s="1" t="s">
         <v>971</v>
       </c>
-      <c r="B463" s="1" t="s">
-        <v>972</v>
-      </c>
       <c r="C463" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D463" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E463" s="1" t="s">
         <v>34</v>
@@ -14128,16 +14125,16 @@
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="B464" s="1" t="s">
         <v>973</v>
       </c>
-      <c r="B464" s="1" t="s">
-        <v>974</v>
-      </c>
       <c r="C464" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D464" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E464" s="1" t="s">
         <v>37</v>
@@ -14148,16 +14145,16 @@
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="B465" s="1" t="s">
         <v>975</v>
       </c>
-      <c r="B465" s="1" t="s">
-        <v>976</v>
-      </c>
       <c r="C465" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D465" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E465" s="1" t="s">
         <v>66</v>
@@ -14168,16 +14165,16 @@
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="B466" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="B466" s="1" t="s">
-        <v>978</v>
-      </c>
       <c r="C466" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D466" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E466" s="1" t="s">
         <v>98</v>
@@ -14188,16 +14185,16 @@
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="B467" s="1" t="s">
         <v>979</v>
       </c>
-      <c r="B467" s="1" t="s">
-        <v>980</v>
-      </c>
       <c r="C467" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D467" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E467" s="1" t="s">
         <v>101</v>
@@ -14208,16 +14205,16 @@
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="B468" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="B468" s="1" t="s">
+      <c r="C468" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D468" s="1" t="s">
         <v>982</v>
-      </c>
-      <c r="C468" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D468" s="1" t="s">
-        <v>983</v>
       </c>
       <c r="E468" s="1" t="s">
         <v>4</v>
@@ -14228,16 +14225,16 @@
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="B469" s="1" t="s">
         <v>984</v>
       </c>
-      <c r="B469" s="1" t="s">
-        <v>985</v>
-      </c>
       <c r="C469" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D469" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E469" s="1" t="s">
         <v>8</v>
@@ -14248,56 +14245,56 @@
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="B470" s="1" t="s">
         <v>986</v>
       </c>
-      <c r="B470" s="1" t="s">
-        <v>987</v>
-      </c>
       <c r="C470" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D470" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E470" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F470" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="B471" s="1" t="s">
         <v>989</v>
       </c>
-      <c r="B471" s="1" t="s">
-        <v>990</v>
-      </c>
       <c r="C471" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D471" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E471" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F471" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="B472" s="1" t="s">
         <v>991</v>
       </c>
-      <c r="B472" s="1" t="s">
-        <v>992</v>
-      </c>
       <c r="C472" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D472" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E472" s="1" t="s">
         <v>18</v>
@@ -14308,16 +14305,16 @@
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="B473" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="B473" s="1" t="s">
-        <v>994</v>
-      </c>
       <c r="C473" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D473" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E473" s="1" t="s">
         <v>21</v>
@@ -14328,16 +14325,16 @@
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="B474" s="1" t="s">
         <v>995</v>
       </c>
-      <c r="B474" s="1" t="s">
-        <v>996</v>
-      </c>
       <c r="C474" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D474" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E474" s="1" t="s">
         <v>24</v>
@@ -14348,16 +14345,16 @@
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="B475" s="1" t="s">
         <v>997</v>
       </c>
-      <c r="B475" s="1" t="s">
-        <v>998</v>
-      </c>
       <c r="C475" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D475" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E475" s="1" t="s">
         <v>55</v>
@@ -14368,16 +14365,16 @@
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="B476" s="1" t="s">
         <v>999</v>
       </c>
-      <c r="B476" s="1" t="s">
-        <v>1000</v>
-      </c>
       <c r="C476" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D476" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E476" s="1" t="s">
         <v>28</v>
@@ -14388,16 +14385,16 @@
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B477" s="1" t="s">
         <v>1001</v>
       </c>
-      <c r="B477" s="1" t="s">
-        <v>1002</v>
-      </c>
       <c r="C477" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D477" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E477" s="1" t="s">
         <v>31</v>
@@ -14408,16 +14405,16 @@
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B478" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="B478" s="1" t="s">
-        <v>1004</v>
-      </c>
       <c r="C478" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D478" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E478" s="1" t="s">
         <v>34</v>
@@ -14428,16 +14425,16 @@
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B479" s="1" t="s">
         <v>1005</v>
       </c>
-      <c r="B479" s="1" t="s">
-        <v>1006</v>
-      </c>
       <c r="C479" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D479" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E479" s="1" t="s">
         <v>37</v>
@@ -14448,16 +14445,16 @@
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B480" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="B480" s="1" t="s">
-        <v>1008</v>
-      </c>
       <c r="C480" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D480" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E480" s="1" t="s">
         <v>66</v>
@@ -14468,16 +14465,16 @@
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B481" s="1" t="s">
         <v>1009</v>
       </c>
-      <c r="B481" s="1" t="s">
-        <v>1010</v>
-      </c>
       <c r="C481" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D481" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E481" s="1" t="s">
         <v>98</v>
@@ -14488,16 +14485,16 @@
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B482" s="1" t="s">
         <v>1011</v>
       </c>
-      <c r="B482" s="1" t="s">
-        <v>1012</v>
-      </c>
       <c r="C482" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D482" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E482" s="1" t="s">
         <v>101</v>
@@ -14508,16 +14505,16 @@
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B483" s="1" t="s">
         <v>1013</v>
       </c>
-      <c r="B483" s="1" t="s">
-        <v>1014</v>
-      </c>
       <c r="C483" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D483" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E483" s="1" t="s">
         <v>104</v>
@@ -14528,16 +14525,16 @@
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B484" s="1" t="s">
         <v>1015</v>
       </c>
-      <c r="B484" s="1" t="s">
+      <c r="C484" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D484" s="1" t="s">
         <v>1016</v>
-      </c>
-      <c r="C484" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D484" s="1" t="s">
-        <v>1017</v>
       </c>
       <c r="E484" s="1" t="s">
         <v>4</v>
@@ -14548,16 +14545,16 @@
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B485" s="1" t="s">
         <v>1018</v>
       </c>
-      <c r="B485" s="1" t="s">
-        <v>1019</v>
-      </c>
       <c r="C485" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D485" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E485" s="1" t="s">
         <v>8</v>
@@ -14568,16 +14565,16 @@
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B486" s="1" t="s">
         <v>1020</v>
       </c>
-      <c r="B486" s="1" t="s">
-        <v>1021</v>
-      </c>
       <c r="C486" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D486" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>12</v>
@@ -14588,16 +14585,16 @@
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B487" s="1" t="s">
         <v>1022</v>
       </c>
-      <c r="B487" s="1" t="s">
-        <v>1023</v>
-      </c>
       <c r="C487" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D487" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E487" s="1" t="s">
         <v>15</v>
@@ -14608,16 +14605,16 @@
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B488" s="1" t="s">
         <v>1024</v>
       </c>
-      <c r="B488" s="1" t="s">
-        <v>1025</v>
-      </c>
       <c r="C488" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D488" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E488" s="1" t="s">
         <v>18</v>
@@ -14628,16 +14625,16 @@
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B489" s="1" t="s">
         <v>1026</v>
       </c>
-      <c r="B489" s="1" t="s">
-        <v>1027</v>
-      </c>
       <c r="C489" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D489" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E489" s="1" t="s">
         <v>21</v>
@@ -14648,16 +14645,16 @@
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B490" s="1" t="s">
         <v>1028</v>
       </c>
-      <c r="B490" s="1" t="s">
-        <v>1029</v>
-      </c>
       <c r="C490" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D490" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E490" s="1" t="s">
         <v>24</v>
@@ -14668,16 +14665,16 @@
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B491" s="1" t="s">
         <v>1030</v>
       </c>
-      <c r="B491" s="1" t="s">
-        <v>1031</v>
-      </c>
       <c r="C491" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D491" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E491" s="1" t="s">
         <v>55</v>
@@ -14688,16 +14685,16 @@
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B492" s="1" t="s">
         <v>1032</v>
       </c>
-      <c r="B492" s="1" t="s">
-        <v>1033</v>
-      </c>
       <c r="C492" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D492" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E492" s="1" t="s">
         <v>28</v>
@@ -14708,36 +14705,36 @@
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B493" s="1" t="s">
         <v>1034</v>
       </c>
-      <c r="B493" s="1" t="s">
-        <v>1035</v>
-      </c>
       <c r="C493" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D493" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E493" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F493" s="1" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B494" s="1" t="s">
         <v>1037</v>
       </c>
-      <c r="B494" s="1" t="s">
-        <v>1038</v>
-      </c>
       <c r="C494" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D494" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E494" s="1" t="s">
         <v>34</v>
@@ -14748,16 +14745,16 @@
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B495" s="1" t="s">
         <v>1039</v>
       </c>
-      <c r="B495" s="1" t="s">
-        <v>1040</v>
-      </c>
       <c r="C495" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D495" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E495" s="1" t="s">
         <v>37</v>
@@ -14768,16 +14765,16 @@
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B496" s="1" t="s">
         <v>1041</v>
       </c>
-      <c r="B496" s="1" t="s">
-        <v>1042</v>
-      </c>
       <c r="C496" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D496" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E496" s="1" t="s">
         <v>66</v>
@@ -14788,16 +14785,16 @@
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B497" s="1" t="s">
         <v>1043</v>
       </c>
-      <c r="B497" s="1" t="s">
-        <v>1044</v>
-      </c>
       <c r="C497" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D497" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E497" s="1" t="s">
         <v>98</v>
@@ -14808,16 +14805,16 @@
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B498" s="1" t="s">
         <v>1045</v>
       </c>
-      <c r="B498" s="1" t="s">
-        <v>1046</v>
-      </c>
       <c r="C498" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D498" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E498" s="1" t="s">
         <v>101</v>
@@ -14828,16 +14825,16 @@
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B499" s="1" t="s">
         <v>1047</v>
       </c>
-      <c r="B499" s="1" t="s">
-        <v>1048</v>
-      </c>
       <c r="C499" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D499" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E499" s="1" t="s">
         <v>104</v>
@@ -14848,16 +14845,16 @@
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B500" s="1" t="s">
         <v>1049</v>
       </c>
-      <c r="B500" s="1" t="s">
-        <v>1050</v>
-      </c>
       <c r="C500" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D500" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E500" s="1" t="s">
         <v>107</v>
@@ -14868,16 +14865,16 @@
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B501" s="1" t="s">
         <v>1051</v>
       </c>
-      <c r="B501" s="1" t="s">
-        <v>1052</v>
-      </c>
       <c r="C501" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D501" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E501" s="1" t="s">
         <v>110</v>
@@ -14888,16 +14885,16 @@
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B502" s="1" t="s">
         <v>1053</v>
       </c>
-      <c r="B502" s="1" t="s">
+      <c r="C502" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D502" s="1" t="s">
         <v>1054</v>
-      </c>
-      <c r="C502" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D502" s="1" t="s">
-        <v>1055</v>
       </c>
       <c r="E502" s="1" t="s">
         <v>4</v>
@@ -14908,16 +14905,16 @@
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B503" s="1" t="s">
         <v>1056</v>
       </c>
-      <c r="B503" s="1" t="s">
-        <v>1057</v>
-      </c>
       <c r="C503" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D503" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E503" s="1" t="s">
         <v>8</v>
@@ -14928,16 +14925,16 @@
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B504" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="B504" s="1" t="s">
-        <v>1059</v>
-      </c>
       <c r="C504" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D504" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E504" s="1" t="s">
         <v>12</v>
@@ -14948,16 +14945,16 @@
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B505" s="1" t="s">
         <v>1060</v>
       </c>
-      <c r="B505" s="1" t="s">
-        <v>1061</v>
-      </c>
       <c r="C505" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D505" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E505" s="1" t="s">
         <v>15</v>
@@ -14968,16 +14965,16 @@
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B506" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="B506" s="1" t="s">
-        <v>1063</v>
-      </c>
       <c r="C506" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D506" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E506" s="1" t="s">
         <v>18</v>
@@ -14988,16 +14985,16 @@
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B507" s="1" t="s">
         <v>1064</v>
       </c>
-      <c r="B507" s="1" t="s">
-        <v>1065</v>
-      </c>
       <c r="C507" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D507" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E507" s="1" t="s">
         <v>21</v>
@@ -15008,16 +15005,16 @@
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B508" s="1" t="s">
         <v>1066</v>
       </c>
-      <c r="B508" s="1" t="s">
-        <v>1067</v>
-      </c>
       <c r="C508" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D508" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E508" s="1" t="s">
         <v>24</v>
@@ -15028,16 +15025,16 @@
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B509" s="1" t="s">
         <v>1068</v>
       </c>
-      <c r="B509" s="1" t="s">
-        <v>1069</v>
-      </c>
       <c r="C509" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D509" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E509" s="1" t="s">
         <v>55</v>
@@ -15048,16 +15045,16 @@
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B510" s="1" t="s">
         <v>1070</v>
       </c>
-      <c r="B510" s="1" t="s">
-        <v>1071</v>
-      </c>
       <c r="C510" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D510" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E510" s="1" t="s">
         <v>28</v>
@@ -15068,16 +15065,16 @@
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B511" s="1" t="s">
         <v>1072</v>
       </c>
-      <c r="B511" s="1" t="s">
-        <v>1073</v>
-      </c>
       <c r="C511" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D511" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E511" s="1" t="s">
         <v>31</v>
@@ -15088,16 +15085,16 @@
     </row>
     <row r="512" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B512" s="1" t="s">
         <v>1074</v>
       </c>
-      <c r="B512" s="1" t="s">
-        <v>1075</v>
-      </c>
       <c r="C512" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D512" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E512" s="1" t="s">
         <v>34</v>
@@ -15108,36 +15105,36 @@
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B513" s="1" t="s">
         <v>1076</v>
       </c>
-      <c r="B513" s="1" t="s">
-        <v>1077</v>
-      </c>
       <c r="C513" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D513" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E513" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F513" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B514" s="1" t="s">
         <v>1079</v>
       </c>
-      <c r="B514" s="1" t="s">
-        <v>1080</v>
-      </c>
       <c r="C514" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D514" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E514" s="1" t="s">
         <v>66</v>
@@ -15148,16 +15145,16 @@
     </row>
     <row r="515" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B515" s="1" t="s">
         <v>1081</v>
       </c>
-      <c r="B515" s="1" t="s">
-        <v>1082</v>
-      </c>
       <c r="C515" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D515" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E515" s="1" t="s">
         <v>98</v>
@@ -15168,16 +15165,16 @@
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B516" s="1" t="s">
         <v>1083</v>
       </c>
-      <c r="B516" s="1" t="s">
-        <v>1084</v>
-      </c>
       <c r="C516" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D516" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E516" s="1" t="s">
         <v>101</v>
@@ -15188,16 +15185,16 @@
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B517" s="1" t="s">
         <v>1085</v>
       </c>
-      <c r="B517" s="1" t="s">
+      <c r="C517" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D517" s="1" t="s">
         <v>1086</v>
-      </c>
-      <c r="C517" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D517" s="1" t="s">
-        <v>1087</v>
       </c>
       <c r="E517" s="1" t="s">
         <v>4</v>
@@ -15208,16 +15205,16 @@
     </row>
     <row r="518" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B518" s="1" t="s">
         <v>1088</v>
       </c>
-      <c r="B518" s="1" t="s">
-        <v>1089</v>
-      </c>
       <c r="C518" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D518" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E518" s="1" t="s">
         <v>4</v>
@@ -15228,16 +15225,16 @@
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B519" s="1" t="s">
         <v>1090</v>
       </c>
-      <c r="B519" s="1" t="s">
-        <v>1091</v>
-      </c>
       <c r="C519" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D519" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E519" s="1" t="s">
         <v>4</v>
@@ -15248,16 +15245,16 @@
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B520" s="1" t="s">
         <v>1092</v>
       </c>
-      <c r="B520" s="1" t="s">
-        <v>1093</v>
-      </c>
       <c r="C520" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D520" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E520" s="1" t="s">
         <v>8</v>
@@ -15268,16 +15265,16 @@
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B521" s="1" t="s">
         <v>1094</v>
       </c>
-      <c r="B521" s="1" t="s">
-        <v>1095</v>
-      </c>
       <c r="C521" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D521" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E521" s="1" t="s">
         <v>8</v>
@@ -15288,16 +15285,16 @@
     </row>
     <row r="522" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B522" s="1" t="s">
         <v>1096</v>
       </c>
-      <c r="B522" s="1" t="s">
-        <v>1097</v>
-      </c>
       <c r="C522" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D522" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E522" s="1" t="s">
         <v>8</v>
@@ -15308,16 +15305,16 @@
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B523" s="1" t="s">
         <v>1098</v>
       </c>
-      <c r="B523" s="1" t="s">
-        <v>1099</v>
-      </c>
       <c r="C523" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D523" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E523" s="1" t="s">
         <v>12</v>
@@ -15328,16 +15325,16 @@
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B524" s="1" t="s">
         <v>1100</v>
       </c>
-      <c r="B524" s="1" t="s">
-        <v>1101</v>
-      </c>
       <c r="C524" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D524" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E524" s="1" t="s">
         <v>12</v>
@@ -15348,16 +15345,16 @@
     </row>
     <row r="525" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B525" s="1" t="s">
         <v>1102</v>
       </c>
-      <c r="B525" s="1" t="s">
-        <v>1103</v>
-      </c>
       <c r="C525" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D525" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E525" s="1" t="s">
         <v>12</v>
@@ -15368,16 +15365,16 @@
     </row>
     <row r="526" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B526" s="1" t="s">
         <v>1104</v>
       </c>
-      <c r="B526" s="1" t="s">
-        <v>1105</v>
-      </c>
       <c r="C526" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D526" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E526" s="1" t="s">
         <v>15</v>
@@ -15388,16 +15385,16 @@
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B527" s="1" t="s">
         <v>1106</v>
       </c>
-      <c r="B527" s="1" t="s">
-        <v>1107</v>
-      </c>
       <c r="C527" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D527" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E527" s="1" t="s">
         <v>15</v>
@@ -15408,16 +15405,16 @@
     </row>
     <row r="528" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B528" s="1" t="s">
         <v>1108</v>
       </c>
-      <c r="B528" s="1" t="s">
-        <v>1109</v>
-      </c>
       <c r="C528" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D528" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E528" s="1" t="s">
         <v>15</v>
@@ -15428,16 +15425,16 @@
     </row>
     <row r="529" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B529" s="1" t="s">
         <v>1110</v>
       </c>
-      <c r="B529" s="1" t="s">
-        <v>1111</v>
-      </c>
       <c r="C529" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D529" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E529" s="1" t="s">
         <v>18</v>
@@ -15448,16 +15445,16 @@
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B530" s="1" t="s">
         <v>1112</v>
       </c>
-      <c r="B530" s="1" t="s">
-        <v>1113</v>
-      </c>
       <c r="C530" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D530" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E530" s="1" t="s">
         <v>18</v>
@@ -15468,16 +15465,16 @@
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B531" s="1" t="s">
         <v>1114</v>
       </c>
-      <c r="B531" s="1" t="s">
-        <v>1115</v>
-      </c>
       <c r="C531" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D531" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E531" s="1" t="s">
         <v>18</v>
@@ -15488,16 +15485,16 @@
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B532" s="1" t="s">
         <v>1116</v>
       </c>
-      <c r="B532" s="1" t="s">
-        <v>1117</v>
-      </c>
       <c r="C532" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D532" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E532" s="1" t="s">
         <v>21</v>
@@ -15508,16 +15505,16 @@
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B533" s="1" t="s">
         <v>1118</v>
       </c>
-      <c r="B533" s="1" t="s">
-        <v>1119</v>
-      </c>
       <c r="C533" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D533" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E533" s="1" t="s">
         <v>21</v>
@@ -15528,16 +15525,16 @@
     </row>
     <row r="534" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B534" s="1" t="s">
         <v>1120</v>
       </c>
-      <c r="B534" s="1" t="s">
-        <v>1121</v>
-      </c>
       <c r="C534" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D534" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E534" s="1" t="s">
         <v>21</v>
@@ -15548,16 +15545,16 @@
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B535" s="1" t="s">
         <v>1122</v>
       </c>
-      <c r="B535" s="1" t="s">
-        <v>1123</v>
-      </c>
       <c r="C535" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D535" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E535" s="1" t="s">
         <v>24</v>
@@ -15568,16 +15565,16 @@
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B536" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="B536" s="1" t="s">
-        <v>1125</v>
-      </c>
       <c r="C536" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D536" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E536" s="1" t="s">
         <v>24</v>
@@ -15588,16 +15585,16 @@
     </row>
     <row r="537" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B537" s="1" t="s">
         <v>1126</v>
       </c>
-      <c r="B537" s="1" t="s">
-        <v>1127</v>
-      </c>
       <c r="C537" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D537" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E537" s="1" t="s">
         <v>55</v>
@@ -15608,16 +15605,16 @@
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B538" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="B538" s="1" t="s">
-        <v>1129</v>
-      </c>
       <c r="C538" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D538" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E538" s="1" t="s">
         <v>55</v>
@@ -15628,16 +15625,16 @@
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B539" s="1" t="s">
         <v>1130</v>
       </c>
-      <c r="B539" s="1" t="s">
-        <v>1131</v>
-      </c>
       <c r="C539" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D539" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E539" s="1" t="s">
         <v>55</v>
@@ -15648,16 +15645,16 @@
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B540" s="1" t="s">
         <v>1132</v>
       </c>
-      <c r="B540" s="1" t="s">
-        <v>1133</v>
-      </c>
       <c r="C540" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D540" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E540" s="1" t="s">
         <v>28</v>
@@ -15668,16 +15665,16 @@
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B541" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="B541" s="1" t="s">
-        <v>1135</v>
-      </c>
       <c r="C541" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D541" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E541" s="1" t="s">
         <v>28</v>
@@ -15688,16 +15685,16 @@
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B542" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B542" s="1" t="s">
-        <v>1137</v>
-      </c>
       <c r="C542" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D542" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E542" s="1" t="s">
         <v>28</v>
@@ -15708,16 +15705,16 @@
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B543" s="1" t="s">
         <v>1138</v>
       </c>
-      <c r="B543" s="1" t="s">
-        <v>1139</v>
-      </c>
       <c r="C543" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D543" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E543" s="1" t="s">
         <v>31</v>
@@ -15728,16 +15725,16 @@
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B544" s="1" t="s">
         <v>1140</v>
       </c>
-      <c r="B544" s="1" t="s">
-        <v>1141</v>
-      </c>
       <c r="C544" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D544" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E544" s="1" t="s">
         <v>31</v>
@@ -15748,16 +15745,16 @@
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B545" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="B545" s="1" t="s">
-        <v>1143</v>
-      </c>
       <c r="C545" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D545" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E545" s="1" t="s">
         <v>31</v>
@@ -15768,16 +15765,16 @@
     </row>
     <row r="546" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B546" s="1" t="s">
         <v>1144</v>
       </c>
-      <c r="B546" s="1" t="s">
-        <v>1145</v>
-      </c>
       <c r="C546" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D546" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E546" s="1" t="s">
         <v>34</v>
@@ -15788,16 +15785,16 @@
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B547" s="1" t="s">
         <v>1146</v>
       </c>
-      <c r="B547" s="1" t="s">
-        <v>1147</v>
-      </c>
       <c r="C547" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D547" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E547" s="1" t="s">
         <v>34</v>
@@ -15808,16 +15805,16 @@
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B548" s="1" t="s">
         <v>1148</v>
       </c>
-      <c r="B548" s="1" t="s">
-        <v>1149</v>
-      </c>
       <c r="C548" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D548" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E548" s="1" t="s">
         <v>37</v>
@@ -15828,16 +15825,16 @@
     </row>
     <row r="549" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B549" s="1" t="s">
         <v>1150</v>
       </c>
-      <c r="B549" s="1" t="s">
-        <v>1151</v>
-      </c>
       <c r="C549" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D549" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E549" s="1" t="s">
         <v>37</v>
@@ -15848,16 +15845,16 @@
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B550" s="1" t="s">
         <v>1152</v>
       </c>
-      <c r="B550" s="1" t="s">
-        <v>1153</v>
-      </c>
       <c r="C550" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D550" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E550" s="1" t="s">
         <v>66</v>
@@ -15868,16 +15865,16 @@
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B551" s="1" t="s">
         <v>1154</v>
       </c>
-      <c r="B551" s="1" t="s">
-        <v>1155</v>
-      </c>
       <c r="C551" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D551" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E551" s="1" t="s">
         <v>98</v>
@@ -15888,16 +15885,16 @@
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B552" s="1" t="s">
         <v>1156</v>
       </c>
-      <c r="B552" s="1" t="s">
-        <v>1157</v>
-      </c>
       <c r="C552" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D552" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E552" s="1" t="s">
         <v>101</v>
@@ -15908,16 +15905,16 @@
     </row>
     <row r="553" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B553" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="B553" s="1" t="s">
-        <v>1159</v>
-      </c>
       <c r="C553" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D553" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E553" s="1" t="s">
         <v>104</v>
@@ -15928,36 +15925,36 @@
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B554" s="1" t="s">
         <v>1160</v>
       </c>
-      <c r="B554" s="1" t="s">
+      <c r="C554" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D554" s="1" t="s">
         <v>1161</v>
-      </c>
-      <c r="C554" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D554" s="1" t="s">
-        <v>1162</v>
       </c>
       <c r="E554" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F554" s="1" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B555" s="1" t="s">
         <v>1164</v>
       </c>
-      <c r="B555" s="1" t="s">
-        <v>1165</v>
-      </c>
       <c r="C555" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D555" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E555" s="1" t="s">
         <v>8</v>
@@ -15968,16 +15965,16 @@
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B556" s="1" t="s">
         <v>1166</v>
       </c>
-      <c r="B556" s="1" t="s">
-        <v>1167</v>
-      </c>
       <c r="C556" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D556" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E556" s="1" t="s">
         <v>12</v>
@@ -15988,16 +15985,16 @@
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B557" s="1" t="s">
         <v>1168</v>
       </c>
-      <c r="B557" s="1" t="s">
-        <v>1169</v>
-      </c>
       <c r="C557" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D557" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E557" s="1" t="s">
         <v>15</v>
@@ -16008,16 +16005,16 @@
     </row>
     <row r="558" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B558" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="B558" s="1" t="s">
-        <v>1171</v>
-      </c>
       <c r="C558" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D558" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E558" s="1" t="s">
         <v>18</v>
@@ -16028,16 +16025,16 @@
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B559" s="1" t="s">
         <v>1172</v>
       </c>
-      <c r="B559" s="1" t="s">
-        <v>1173</v>
-      </c>
       <c r="C559" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D559" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E559" s="1" t="s">
         <v>21</v>
@@ -16048,16 +16045,16 @@
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B560" s="1" t="s">
         <v>1174</v>
       </c>
-      <c r="B560" s="1" t="s">
-        <v>1175</v>
-      </c>
       <c r="C560" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D560" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E560" s="1" t="s">
         <v>24</v>
@@ -16068,16 +16065,16 @@
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B561" s="1" t="s">
         <v>1176</v>
       </c>
-      <c r="B561" s="1" t="s">
-        <v>1177</v>
-      </c>
       <c r="C561" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D561" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E561" s="1" t="s">
         <v>55</v>
@@ -16088,16 +16085,16 @@
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B562" s="1" t="s">
         <v>1178</v>
       </c>
-      <c r="B562" s="1" t="s">
-        <v>1179</v>
-      </c>
       <c r="C562" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D562" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E562" s="1" t="s">
         <v>28</v>
@@ -16108,16 +16105,16 @@
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B563" s="1" t="s">
         <v>1180</v>
       </c>
-      <c r="B563" s="1" t="s">
-        <v>1181</v>
-      </c>
       <c r="C563" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D563" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E563" s="1" t="s">
         <v>31</v>
@@ -16128,16 +16125,16 @@
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B564" s="1" t="s">
         <v>1182</v>
       </c>
-      <c r="B564" s="1" t="s">
-        <v>1183</v>
-      </c>
       <c r="C564" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D564" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E564" s="1" t="s">
         <v>34</v>
@@ -16148,16 +16145,16 @@
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B565" s="1" t="s">
         <v>1184</v>
       </c>
-      <c r="B565" s="1" t="s">
-        <v>1185</v>
-      </c>
       <c r="C565" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D565" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E565" s="1" t="s">
         <v>37</v>
@@ -16168,16 +16165,16 @@
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B566" s="1" t="s">
         <v>1186</v>
       </c>
-      <c r="B566" s="1" t="s">
-        <v>1187</v>
-      </c>
       <c r="C566" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D566" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E566" s="1" t="s">
         <v>66</v>
@@ -16188,16 +16185,16 @@
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B567" s="1" t="s">
         <v>1188</v>
       </c>
-      <c r="B567" s="1" t="s">
-        <v>1189</v>
-      </c>
       <c r="C567" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D567" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E567" s="1" t="s">
         <v>98</v>
@@ -16208,16 +16205,16 @@
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B568" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="B568" s="1" t="s">
+      <c r="C568" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D568" s="1" t="s">
         <v>1191</v>
-      </c>
-      <c r="C568" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D568" s="1" t="s">
-        <v>1192</v>
       </c>
       <c r="E568" s="1" t="s">
         <v>4</v>
@@ -16228,16 +16225,16 @@
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B569" s="1" t="s">
         <v>1193</v>
       </c>
-      <c r="B569" s="1" t="s">
-        <v>1194</v>
-      </c>
       <c r="C569" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D569" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E569" s="1" t="s">
         <v>8</v>
@@ -16248,16 +16245,16 @@
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B570" s="1" t="s">
         <v>1195</v>
       </c>
-      <c r="B570" s="1" t="s">
-        <v>1196</v>
-      </c>
       <c r="C570" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D570" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E570" s="1" t="s">
         <v>12</v>
@@ -16268,16 +16265,16 @@
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B571" s="1" t="s">
         <v>1197</v>
       </c>
-      <c r="B571" s="1" t="s">
-        <v>1198</v>
-      </c>
       <c r="C571" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D571" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E571" s="1" t="s">
         <v>15</v>
@@ -16288,16 +16285,16 @@
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B572" s="1" t="s">
         <v>1199</v>
       </c>
-      <c r="B572" s="1" t="s">
-        <v>1200</v>
-      </c>
       <c r="C572" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D572" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E572" s="1" t="s">
         <v>18</v>
@@ -16308,16 +16305,16 @@
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B573" s="1" t="s">
         <v>1201</v>
       </c>
-      <c r="B573" s="1" t="s">
-        <v>1202</v>
-      </c>
       <c r="C573" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D573" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E573" s="1" t="s">
         <v>21</v>
@@ -16328,16 +16325,16 @@
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B574" s="1" t="s">
         <v>1203</v>
       </c>
-      <c r="B574" s="1" t="s">
-        <v>1204</v>
-      </c>
       <c r="C574" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D574" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E574" s="1" t="s">
         <v>24</v>
@@ -16348,16 +16345,16 @@
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B575" s="1" t="s">
         <v>1205</v>
       </c>
-      <c r="B575" s="1" t="s">
-        <v>1206</v>
-      </c>
       <c r="C575" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D575" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E575" s="1" t="s">
         <v>55</v>
@@ -16368,16 +16365,16 @@
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B576" s="1" t="s">
         <v>1207</v>
       </c>
-      <c r="B576" s="1" t="s">
-        <v>1208</v>
-      </c>
       <c r="C576" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D576" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E576" s="1" t="s">
         <v>28</v>
@@ -16388,16 +16385,16 @@
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B577" s="1" t="s">
         <v>1209</v>
       </c>
-      <c r="B577" s="1" t="s">
-        <v>1210</v>
-      </c>
       <c r="C577" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D577" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E577" s="1" t="s">
         <v>31</v>
@@ -16408,16 +16405,16 @@
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B578" s="1" t="s">
         <v>1211</v>
       </c>
-      <c r="B578" s="1" t="s">
-        <v>1212</v>
-      </c>
       <c r="C578" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D578" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E578" s="1" t="s">
         <v>34</v>
@@ -16428,16 +16425,16 @@
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B579" s="1" t="s">
         <v>1213</v>
       </c>
-      <c r="B579" s="1" t="s">
-        <v>1214</v>
-      </c>
       <c r="C579" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D579" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E579" s="1" t="s">
         <v>37</v>
@@ -16448,16 +16445,16 @@
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B580" s="1" t="s">
         <v>1215</v>
       </c>
-      <c r="B580" s="1" t="s">
-        <v>1216</v>
-      </c>
       <c r="C580" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D580" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E580" s="1" t="s">
         <v>66</v>
@@ -16468,16 +16465,16 @@
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B581" s="1" t="s">
         <v>1217</v>
       </c>
-      <c r="B581" s="1" t="s">
-        <v>1218</v>
-      </c>
       <c r="C581" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D581" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E581" s="1" t="s">
         <v>98</v>
@@ -16488,16 +16485,16 @@
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B582" s="1" t="s">
         <v>1219</v>
       </c>
-      <c r="B582" s="1" t="s">
+      <c r="C582" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D582" s="1" t="s">
         <v>1220</v>
-      </c>
-      <c r="C582" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D582" s="1" t="s">
-        <v>1221</v>
       </c>
       <c r="E582" s="1" t="s">
         <v>4</v>
@@ -16508,16 +16505,16 @@
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B583" s="1" t="s">
         <v>1222</v>
       </c>
-      <c r="B583" s="1" t="s">
-        <v>1223</v>
-      </c>
       <c r="C583" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D583" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E583" s="1" t="s">
         <v>8</v>
@@ -16528,56 +16525,56 @@
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B584" s="1" t="s">
         <v>1224</v>
       </c>
-      <c r="B584" s="1" t="s">
-        <v>1225</v>
-      </c>
       <c r="C584" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D584" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E584" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F584" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B585" s="1" t="s">
         <v>1226</v>
       </c>
-      <c r="B585" s="1" t="s">
-        <v>1227</v>
-      </c>
       <c r="C585" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D585" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E585" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F585" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B586" s="1" t="s">
         <v>1228</v>
       </c>
-      <c r="B586" s="1" t="s">
-        <v>1229</v>
-      </c>
       <c r="C586" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D586" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E586" s="1" t="s">
         <v>18</v>
@@ -16588,16 +16585,16 @@
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B587" s="1" t="s">
         <v>1230</v>
       </c>
-      <c r="B587" s="1" t="s">
-        <v>1231</v>
-      </c>
       <c r="C587" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D587" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E587" s="1" t="s">
         <v>21</v>
@@ -16608,16 +16605,16 @@
     </row>
     <row r="588" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B588" s="1" t="s">
         <v>1232</v>
       </c>
-      <c r="B588" s="1" t="s">
-        <v>1233</v>
-      </c>
       <c r="C588" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D588" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E588" s="1" t="s">
         <v>24</v>
@@ -16628,16 +16625,16 @@
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B589" s="1" t="s">
         <v>1234</v>
       </c>
-      <c r="B589" s="1" t="s">
-        <v>1235</v>
-      </c>
       <c r="C589" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D589" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E589" s="1" t="s">
         <v>55</v>
@@ -16648,16 +16645,16 @@
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B590" s="1" t="s">
         <v>1236</v>
       </c>
-      <c r="B590" s="1" t="s">
-        <v>1237</v>
-      </c>
       <c r="C590" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D590" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E590" s="1" t="s">
         <v>28</v>
@@ -16668,16 +16665,16 @@
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B591" s="1" t="s">
         <v>1238</v>
       </c>
-      <c r="B591" s="1" t="s">
-        <v>1239</v>
-      </c>
       <c r="C591" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D591" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E591" s="1" t="s">
         <v>31</v>
@@ -16688,16 +16685,16 @@
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B592" s="1" t="s">
         <v>1240</v>
       </c>
-      <c r="B592" s="1" t="s">
-        <v>1241</v>
-      </c>
       <c r="C592" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D592" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E592" s="1" t="s">
         <v>34</v>
@@ -16708,16 +16705,16 @@
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B593" s="1" t="s">
         <v>1242</v>
       </c>
-      <c r="B593" s="1" t="s">
-        <v>1243</v>
-      </c>
       <c r="C593" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D593" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E593" s="1" t="s">
         <v>37</v>
@@ -16728,16 +16725,16 @@
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B594" s="1" t="s">
         <v>1244</v>
       </c>
-      <c r="B594" s="1" t="s">
-        <v>1245</v>
-      </c>
       <c r="C594" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D594" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E594" s="1" t="s">
         <v>66</v>
@@ -16748,16 +16745,16 @@
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B595" s="1" t="s">
         <v>1246</v>
       </c>
-      <c r="B595" s="1" t="s">
+      <c r="C595" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D595" s="1" t="s">
         <v>1247</v>
-      </c>
-      <c r="C595" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D595" s="1" t="s">
-        <v>1248</v>
       </c>
       <c r="E595" s="1" t="s">
         <v>4</v>
@@ -16768,16 +16765,16 @@
     </row>
     <row r="596" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B596" s="1" t="s">
         <v>1249</v>
       </c>
-      <c r="B596" s="1" t="s">
-        <v>1250</v>
-      </c>
       <c r="C596" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D596" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E596" s="1" t="s">
         <v>8</v>
@@ -16788,16 +16785,16 @@
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B597" s="1" t="s">
         <v>1251</v>
       </c>
-      <c r="B597" s="1" t="s">
-        <v>1252</v>
-      </c>
       <c r="C597" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D597" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E597" s="1" t="s">
         <v>12</v>
@@ -16808,16 +16805,16 @@
     </row>
     <row r="598" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B598" s="1" t="s">
         <v>1253</v>
       </c>
-      <c r="B598" s="1" t="s">
-        <v>1254</v>
-      </c>
       <c r="C598" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D598" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E598" s="1" t="s">
         <v>15</v>
@@ -16828,16 +16825,16 @@
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B599" s="1" t="s">
         <v>1255</v>
       </c>
-      <c r="B599" s="1" t="s">
-        <v>1256</v>
-      </c>
       <c r="C599" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D599" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E599" s="1" t="s">
         <v>18</v>
@@ -16848,16 +16845,16 @@
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B600" s="1" t="s">
         <v>1257</v>
       </c>
-      <c r="B600" s="1" t="s">
-        <v>1258</v>
-      </c>
       <c r="C600" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D600" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E600" s="1" t="s">
         <v>21</v>
@@ -16868,16 +16865,16 @@
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B601" s="1" t="s">
         <v>1259</v>
       </c>
-      <c r="B601" s="1" t="s">
-        <v>1260</v>
-      </c>
       <c r="C601" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D601" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E601" s="1" t="s">
         <v>24</v>
@@ -16888,16 +16885,16 @@
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B602" s="1" t="s">
         <v>1261</v>
       </c>
-      <c r="B602" s="1" t="s">
-        <v>1262</v>
-      </c>
       <c r="C602" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D602" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E602" s="1" t="s">
         <v>55</v>
@@ -16908,16 +16905,16 @@
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B603" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="B603" s="1" t="s">
-        <v>1264</v>
-      </c>
       <c r="C603" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D603" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E603" s="1" t="s">
         <v>28</v>
@@ -16928,16 +16925,16 @@
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B604" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="B604" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="C604" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D604" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E604" s="1" t="s">
         <v>31</v>
@@ -16948,16 +16945,16 @@
     </row>
     <row r="605" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B605" s="1" t="s">
         <v>1267</v>
       </c>
-      <c r="B605" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="C605" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D605" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E605" s="1" t="s">
         <v>34</v>
@@ -16968,16 +16965,16 @@
     </row>
     <row r="606" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B606" s="1" t="s">
         <v>1269</v>
       </c>
-      <c r="B606" s="1" t="s">
-        <v>1270</v>
-      </c>
       <c r="C606" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D606" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E606" s="1" t="s">
         <v>37</v>
@@ -16988,16 +16985,16 @@
     </row>
     <row r="607" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B607" s="1" t="s">
         <v>1271</v>
       </c>
-      <c r="B607" s="1" t="s">
-        <v>1272</v>
-      </c>
       <c r="C607" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D607" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E607" s="1" t="s">
         <v>66</v>
@@ -17008,16 +17005,16 @@
     </row>
     <row r="608" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B608" s="1" t="s">
         <v>1273</v>
       </c>
-      <c r="B608" s="1" t="s">
-        <v>1274</v>
-      </c>
       <c r="C608" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D608" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E608" s="1" t="s">
         <v>98</v>
@@ -17028,16 +17025,16 @@
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B609" s="1" t="s">
         <v>1275</v>
       </c>
-      <c r="B609" s="1" t="s">
-        <v>1276</v>
-      </c>
       <c r="C609" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D609" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E609" s="1" t="s">
         <v>101</v>
@@ -17048,16 +17045,16 @@
     </row>
     <row r="610" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B610" s="1" t="s">
         <v>1277</v>
       </c>
-      <c r="B610" s="1" t="s">
-        <v>1278</v>
-      </c>
       <c r="C610" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D610" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E610" s="1" t="s">
         <v>104</v>
@@ -17068,16 +17065,16 @@
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B611" s="1" t="s">
         <v>1279</v>
       </c>
-      <c r="B611" s="1" t="s">
-        <v>1280</v>
-      </c>
       <c r="C611" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D611" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E611" s="1" t="s">
         <v>107</v>
@@ -17088,16 +17085,16 @@
     </row>
     <row r="612" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B612" s="1" t="s">
         <v>1281</v>
       </c>
-      <c r="B612" s="1" t="s">
+      <c r="C612" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D612" s="1" t="s">
         <v>1282</v>
-      </c>
-      <c r="C612" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D612" s="1" t="s">
-        <v>1283</v>
       </c>
       <c r="E612" s="1" t="s">
         <v>4</v>
@@ -17108,16 +17105,16 @@
     </row>
     <row r="613" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B613" s="1" t="s">
         <v>1284</v>
       </c>
-      <c r="B613" s="1" t="s">
-        <v>1285</v>
-      </c>
       <c r="C613" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D613" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E613" s="1" t="s">
         <v>8</v>
@@ -17128,16 +17125,16 @@
     </row>
     <row r="614" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B614" s="1" t="s">
         <v>1286</v>
       </c>
-      <c r="B614" s="1" t="s">
-        <v>1287</v>
-      </c>
       <c r="C614" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D614" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E614" s="1" t="s">
         <v>12</v>
@@ -17148,16 +17145,16 @@
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B615" s="1" t="s">
         <v>1288</v>
       </c>
-      <c r="B615" s="1" t="s">
-        <v>1289</v>
-      </c>
       <c r="C615" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D615" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E615" s="1" t="s">
         <v>15</v>
@@ -17168,16 +17165,16 @@
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B616" s="1" t="s">
         <v>1290</v>
       </c>
-      <c r="B616" s="1" t="s">
-        <v>1291</v>
-      </c>
       <c r="C616" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D616" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E616" s="1" t="s">
         <v>18</v>
@@ -17188,16 +17185,16 @@
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B617" s="1" t="s">
         <v>1292</v>
       </c>
-      <c r="B617" s="1" t="s">
-        <v>1293</v>
-      </c>
       <c r="C617" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D617" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E617" s="1" t="s">
         <v>21</v>
@@ -17208,16 +17205,16 @@
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B618" s="1" t="s">
         <v>1294</v>
       </c>
-      <c r="B618" s="1" t="s">
-        <v>1295</v>
-      </c>
       <c r="C618" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D618" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E618" s="1" t="s">
         <v>24</v>
@@ -17228,16 +17225,16 @@
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B619" s="1" t="s">
         <v>1296</v>
       </c>
-      <c r="B619" s="1" t="s">
-        <v>1297</v>
-      </c>
       <c r="C619" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D619" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E619" s="1" t="s">
         <v>55</v>
@@ -17248,16 +17245,16 @@
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B620" s="1" t="s">
         <v>1298</v>
       </c>
-      <c r="B620" s="1" t="s">
-        <v>1299</v>
-      </c>
       <c r="C620" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D620" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E620" s="1" t="s">
         <v>28</v>
@@ -17268,16 +17265,16 @@
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B621" s="1" t="s">
         <v>1300</v>
       </c>
-      <c r="B621" s="1" t="s">
-        <v>1301</v>
-      </c>
       <c r="C621" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D621" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E621" s="1" t="s">
         <v>31</v>
@@ -17288,16 +17285,16 @@
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B622" s="1" t="s">
         <v>1302</v>
       </c>
-      <c r="B622" s="1" t="s">
-        <v>1303</v>
-      </c>
       <c r="C622" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D622" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E622" s="1" t="s">
         <v>34</v>
@@ -17308,16 +17305,16 @@
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B623" s="1" t="s">
         <v>1304</v>
       </c>
-      <c r="B623" s="1" t="s">
-        <v>1305</v>
-      </c>
       <c r="C623" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D623" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E623" s="1" t="s">
         <v>37</v>
@@ -17328,16 +17325,16 @@
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B624" s="1" t="s">
         <v>1306</v>
       </c>
-      <c r="B624" s="1" t="s">
-        <v>1307</v>
-      </c>
       <c r="C624" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D624" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E624" s="1" t="s">
         <v>66</v>
@@ -17348,16 +17345,16 @@
     </row>
     <row r="625" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B625" s="1" t="s">
         <v>1308</v>
       </c>
-      <c r="B625" s="1" t="s">
-        <v>1309</v>
-      </c>
       <c r="C625" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D625" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E625" s="1" t="s">
         <v>98</v>
@@ -17368,16 +17365,16 @@
     </row>
     <row r="626" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B626" s="1" t="s">
         <v>1310</v>
       </c>
-      <c r="B626" s="1" t="s">
-        <v>1311</v>
-      </c>
       <c r="C626" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D626" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E626" s="1" t="s">
         <v>101</v>
@@ -17388,16 +17385,16 @@
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B627" s="1" t="s">
         <v>1312</v>
       </c>
-      <c r="B627" s="1" t="s">
-        <v>1313</v>
-      </c>
       <c r="C627" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D627" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E627" s="1" t="s">
         <v>104</v>
@@ -17408,16 +17405,16 @@
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B628" s="1" t="s">
         <v>1314</v>
       </c>
-      <c r="B628" s="1" t="s">
-        <v>1315</v>
-      </c>
       <c r="C628" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D628" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E628" s="1" t="s">
         <v>107</v>
@@ -17428,16 +17425,16 @@
     </row>
     <row r="629" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B629" s="1" t="s">
         <v>1316</v>
       </c>
-      <c r="B629" s="1" t="s">
-        <v>1317</v>
-      </c>
       <c r="C629" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D629" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E629" s="1" t="s">
         <v>110</v>
@@ -17448,16 +17445,16 @@
     </row>
     <row r="630" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B630" s="1" t="s">
         <v>1318</v>
       </c>
-      <c r="B630" s="1" t="s">
+      <c r="C630" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D630" s="1" t="s">
         <v>1319</v>
-      </c>
-      <c r="C630" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D630" s="1" t="s">
-        <v>1320</v>
       </c>
       <c r="E630" s="1" t="s">
         <v>4</v>
@@ -17468,16 +17465,16 @@
     </row>
     <row r="631" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A631" s="1" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B631" s="1" t="s">
         <v>1321</v>
       </c>
-      <c r="B631" s="1" t="s">
-        <v>1322</v>
-      </c>
       <c r="C631" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D631" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E631" s="1" t="s">
         <v>8</v>
@@ -17488,16 +17485,16 @@
     </row>
     <row r="632" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A632" s="1" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B632" s="1" t="s">
         <v>1323</v>
       </c>
-      <c r="B632" s="1" t="s">
-        <v>1324</v>
-      </c>
       <c r="C632" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D632" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E632" s="1" t="s">
         <v>12</v>
@@ -17508,16 +17505,16 @@
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B633" s="1" t="s">
         <v>1325</v>
       </c>
-      <c r="B633" s="1" t="s">
-        <v>1326</v>
-      </c>
       <c r="C633" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D633" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E633" s="1" t="s">
         <v>15</v>
@@ -17528,16 +17525,16 @@
     </row>
     <row r="634" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="B634" s="1" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="C634" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D634" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E634" s="1" t="s">
         <v>18</v>
@@ -17548,16 +17545,16 @@
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B635" s="1" t="s">
         <v>1328</v>
       </c>
-      <c r="B635" s="1" t="s">
-        <v>1329</v>
-      </c>
       <c r="C635" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D635" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E635" s="1" t="s">
         <v>21</v>
@@ -17568,16 +17565,16 @@
     </row>
     <row r="636" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B636" s="1" t="s">
         <v>1330</v>
       </c>
-      <c r="B636" s="1" t="s">
-        <v>1331</v>
-      </c>
       <c r="C636" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D636" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E636" s="1" t="s">
         <v>24</v>
@@ -17588,16 +17585,16 @@
     </row>
     <row r="637" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B637" s="1" t="s">
         <v>1332</v>
       </c>
-      <c r="B637" s="1" t="s">
-        <v>1333</v>
-      </c>
       <c r="C637" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D637" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E637" s="1" t="s">
         <v>55</v>
@@ -17608,16 +17605,16 @@
     </row>
     <row r="638" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B638" s="1" t="s">
         <v>1334</v>
       </c>
-      <c r="B638" s="1" t="s">
-        <v>1335</v>
-      </c>
       <c r="C638" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D638" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E638" s="1" t="s">
         <v>28</v>
@@ -17628,16 +17625,16 @@
     </row>
     <row r="639" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B639" s="1" t="s">
         <v>1336</v>
       </c>
-      <c r="B639" s="1" t="s">
-        <v>1337</v>
-      </c>
       <c r="C639" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D639" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E639" s="1" t="s">
         <v>31</v>
@@ -17648,16 +17645,16 @@
     </row>
     <row r="640" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B640" s="1" t="s">
         <v>1338</v>
       </c>
-      <c r="B640" s="1" t="s">
-        <v>1339</v>
-      </c>
       <c r="C640" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D640" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E640" s="1" t="s">
         <v>34</v>
@@ -17668,16 +17665,16 @@
     </row>
     <row r="641" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B641" s="1" t="s">
         <v>1340</v>
       </c>
-      <c r="B641" s="1" t="s">
-        <v>1341</v>
-      </c>
       <c r="C641" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D641" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E641" s="1" t="s">
         <v>37</v>
@@ -17688,16 +17685,16 @@
     </row>
     <row r="642" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B642" s="1" t="s">
         <v>1342</v>
       </c>
-      <c r="B642" s="1" t="s">
-        <v>1343</v>
-      </c>
       <c r="C642" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D642" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E642" s="1" t="s">
         <v>66</v>
@@ -17708,16 +17705,16 @@
     </row>
     <row r="643" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B643" s="1" t="s">
         <v>1344</v>
       </c>
-      <c r="B643" s="1" t="s">
-        <v>1345</v>
-      </c>
       <c r="C643" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D643" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E643" s="1" t="s">
         <v>98</v>
@@ -17728,16 +17725,16 @@
     </row>
     <row r="644" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B644" s="1" t="s">
         <v>1346</v>
       </c>
-      <c r="B644" s="1" t="s">
-        <v>1347</v>
-      </c>
       <c r="C644" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D644" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E644" s="1" t="s">
         <v>101</v>
@@ -17748,16 +17745,16 @@
     </row>
     <row r="645" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B645" s="1" t="s">
         <v>1348</v>
       </c>
-      <c r="B645" s="1" t="s">
-        <v>1349</v>
-      </c>
       <c r="C645" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D645" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E645" s="1" t="s">
         <v>104</v>
@@ -17768,16 +17765,16 @@
     </row>
     <row r="646" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B646" s="1" t="s">
         <v>1350</v>
       </c>
-      <c r="B646" s="1" t="s">
-        <v>1351</v>
-      </c>
       <c r="C646" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D646" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E646" s="1" t="s">
         <v>107</v>
@@ -17788,16 +17785,16 @@
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B647" s="1" t="s">
         <v>1352</v>
       </c>
-      <c r="B647" s="1" t="s">
+      <c r="C647" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D647" s="1" t="s">
         <v>1353</v>
-      </c>
-      <c r="C647" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D647" s="1" t="s">
-        <v>1354</v>
       </c>
       <c r="E647" s="1" t="s">
         <v>4</v>
@@ -17808,16 +17805,16 @@
     </row>
     <row r="648" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B648" s="1" t="s">
         <v>1355</v>
       </c>
-      <c r="B648" s="1" t="s">
-        <v>1356</v>
-      </c>
       <c r="C648" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D648" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="E648" s="1" t="s">
         <v>8</v>
@@ -17828,16 +17825,16 @@
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B649" s="1" t="s">
         <v>1357</v>
       </c>
-      <c r="B649" s="1" t="s">
-        <v>1358</v>
-      </c>
       <c r="C649" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D649" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="E649" s="1" t="s">
         <v>12</v>
@@ -17848,16 +17845,16 @@
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B650" s="1" t="s">
         <v>1359</v>
       </c>
-      <c r="B650" s="1" t="s">
-        <v>1360</v>
-      </c>
       <c r="C650" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D650" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="E650" s="1" t="s">
         <v>15</v>
@@ -17868,16 +17865,16 @@
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B651" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="B651" s="1" t="s">
-        <v>1362</v>
-      </c>
       <c r="C651" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D651" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="E651" s="1" t="s">
         <v>18</v>
@@ -17888,16 +17885,16 @@
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B652" s="1" t="s">
         <v>1363</v>
       </c>
-      <c r="B652" s="1" t="s">
-        <v>1364</v>
-      </c>
       <c r="C652" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D652" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="E652" s="1" t="s">
         <v>21</v>
@@ -17908,16 +17905,16 @@
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B653" s="1" t="s">
         <v>1365</v>
       </c>
-      <c r="B653" s="1" t="s">
-        <v>1366</v>
-      </c>
       <c r="C653" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D653" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="E653" s="1" t="s">
         <v>24</v>
@@ -17928,16 +17925,16 @@
     </row>
     <row r="654" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B654" s="1" t="s">
         <v>1367</v>
       </c>
-      <c r="B654" s="1" t="s">
-        <v>1368</v>
-      </c>
       <c r="C654" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D654" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="E654" s="1" t="s">
         <v>55</v>
@@ -17948,16 +17945,16 @@
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B655" s="1" t="s">
         <v>1369</v>
       </c>
-      <c r="B655" s="1" t="s">
-        <v>1370</v>
-      </c>
       <c r="C655" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D655" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="E655" s="1" t="s">
         <v>28</v>
@@ -17968,16 +17965,16 @@
     </row>
     <row r="656" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B656" s="1" t="s">
         <v>1371</v>
       </c>
-      <c r="B656" s="1" t="s">
-        <v>1372</v>
-      </c>
       <c r="C656" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D656" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="E656" s="1" t="s">
         <v>31</v>
@@ -17988,16 +17985,16 @@
     </row>
     <row r="657" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B657" s="1" t="s">
         <v>1373</v>
       </c>
-      <c r="B657" s="1" t="s">
+      <c r="C657" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D657" s="1" t="s">
         <v>1374</v>
-      </c>
-      <c r="C657" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D657" s="1" t="s">
-        <v>1375</v>
       </c>
       <c r="E657" s="1" t="s">
         <v>4</v>
@@ -18008,16 +18005,16 @@
     </row>
     <row r="658" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B658" s="1" t="s">
         <v>1376</v>
       </c>
-      <c r="B658" s="1" t="s">
-        <v>1377</v>
-      </c>
       <c r="C658" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D658" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E658" s="1" t="s">
         <v>8</v>
@@ -18028,16 +18025,16 @@
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B659" s="1" t="s">
         <v>1378</v>
       </c>
-      <c r="B659" s="1" t="s">
-        <v>1379</v>
-      </c>
       <c r="C659" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D659" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E659" s="1" t="s">
         <v>12</v>
@@ -18048,16 +18045,16 @@
     </row>
     <row r="660" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B660" s="1" t="s">
         <v>1380</v>
       </c>
-      <c r="B660" s="1" t="s">
-        <v>1381</v>
-      </c>
       <c r="C660" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D660" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E660" s="1" t="s">
         <v>15</v>
@@ -18068,16 +18065,16 @@
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B661" s="1" t="s">
         <v>1382</v>
       </c>
-      <c r="B661" s="1" t="s">
-        <v>1383</v>
-      </c>
       <c r="C661" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D661" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E661" s="1" t="s">
         <v>18</v>
@@ -18088,16 +18085,16 @@
     </row>
     <row r="662" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B662" s="1" t="s">
         <v>1384</v>
       </c>
-      <c r="B662" s="1" t="s">
-        <v>1385</v>
-      </c>
       <c r="C662" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D662" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E662" s="1" t="s">
         <v>21</v>
@@ -18108,16 +18105,16 @@
     </row>
     <row r="663" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B663" s="1" t="s">
         <v>1386</v>
       </c>
-      <c r="B663" s="1" t="s">
-        <v>1387</v>
-      </c>
       <c r="C663" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D663" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E663" s="1" t="s">
         <v>24</v>
@@ -18128,16 +18125,16 @@
     </row>
     <row r="664" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B664" s="1" t="s">
         <v>1388</v>
       </c>
-      <c r="B664" s="1" t="s">
-        <v>1389</v>
-      </c>
       <c r="C664" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D664" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E664" s="1" t="s">
         <v>55</v>
@@ -18148,16 +18145,16 @@
     </row>
     <row r="665" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B665" s="1" t="s">
         <v>1390</v>
       </c>
-      <c r="B665" s="1" t="s">
-        <v>1391</v>
-      </c>
       <c r="C665" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D665" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E665" s="1" t="s">
         <v>28</v>
@@ -18168,16 +18165,16 @@
     </row>
     <row r="666" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B666" s="1" t="s">
         <v>1392</v>
       </c>
-      <c r="B666" s="1" t="s">
-        <v>1393</v>
-      </c>
       <c r="C666" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D666" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E666" s="1" t="s">
         <v>31</v>
@@ -18188,16 +18185,16 @@
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B667" s="1" t="s">
         <v>1394</v>
       </c>
-      <c r="B667" s="1" t="s">
-        <v>1395</v>
-      </c>
       <c r="C667" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D667" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E667" s="1" t="s">
         <v>34</v>
@@ -18208,16 +18205,16 @@
     </row>
     <row r="668" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B668" s="1" t="s">
         <v>1396</v>
       </c>
-      <c r="B668" s="1" t="s">
-        <v>1397</v>
-      </c>
       <c r="C668" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D668" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E668" s="1" t="s">
         <v>34</v>
@@ -18228,16 +18225,16 @@
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B669" s="1" t="s">
         <v>1398</v>
       </c>
-      <c r="B669" s="1" t="s">
-        <v>1399</v>
-      </c>
       <c r="C669" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D669" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E669" s="1" t="s">
         <v>37</v>
@@ -18248,16 +18245,16 @@
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B670" s="1" t="s">
         <v>1400</v>
       </c>
-      <c r="B670" s="1" t="s">
-        <v>1401</v>
-      </c>
       <c r="C670" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D670" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E670" s="1" t="s">
         <v>37</v>
@@ -18268,16 +18265,16 @@
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B671" s="1" t="s">
         <v>1402</v>
       </c>
-      <c r="B671" s="1" t="s">
-        <v>1403</v>
-      </c>
       <c r="C671" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D671" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E671" s="1" t="s">
         <v>66</v>
@@ -18288,16 +18285,16 @@
     </row>
     <row r="672" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B672" s="1" t="s">
         <v>1404</v>
       </c>
-      <c r="B672" s="1" t="s">
+      <c r="C672" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D672" s="1" t="s">
         <v>1405</v>
-      </c>
-      <c r="C672" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D672" s="1" t="s">
-        <v>1406</v>
       </c>
       <c r="E672" s="1" t="s">
         <v>4</v>
@@ -18308,16 +18305,16 @@
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B673" s="1" t="s">
         <v>1407</v>
       </c>
-      <c r="B673" s="1" t="s">
-        <v>1408</v>
-      </c>
       <c r="C673" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D673" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E673" s="1" t="s">
         <v>4</v>
@@ -18328,16 +18325,16 @@
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B674" s="1" t="s">
         <v>1409</v>
       </c>
-      <c r="B674" s="1" t="s">
-        <v>1410</v>
-      </c>
       <c r="C674" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D674" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E674" s="1" t="s">
         <v>8</v>
@@ -18348,16 +18345,16 @@
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B675" s="1" t="s">
         <v>1411</v>
       </c>
-      <c r="B675" s="1" t="s">
-        <v>1412</v>
-      </c>
       <c r="C675" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D675" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E675" s="1" t="s">
         <v>8</v>
@@ -18368,16 +18365,16 @@
     </row>
     <row r="676" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B676" s="1" t="s">
         <v>1413</v>
       </c>
-      <c r="B676" s="1" t="s">
-        <v>1414</v>
-      </c>
       <c r="C676" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D676" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E676" s="1" t="s">
         <v>12</v>
@@ -18388,16 +18385,16 @@
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B677" s="1" t="s">
         <v>1415</v>
       </c>
-      <c r="B677" s="1" t="s">
-        <v>1416</v>
-      </c>
       <c r="C677" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D677" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E677" s="1" t="s">
         <v>12</v>
@@ -18408,16 +18405,16 @@
     </row>
     <row r="678" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B678" s="1" t="s">
         <v>1417</v>
       </c>
-      <c r="B678" s="1" t="s">
-        <v>1418</v>
-      </c>
       <c r="C678" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D678" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E678" s="1" t="s">
         <v>15</v>
@@ -18428,16 +18425,16 @@
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B679" s="1" t="s">
         <v>1419</v>
       </c>
-      <c r="B679" s="1" t="s">
-        <v>1420</v>
-      </c>
       <c r="C679" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D679" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E679" s="1" t="s">
         <v>15</v>
@@ -18448,16 +18445,16 @@
     </row>
     <row r="680" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B680" s="1" t="s">
         <v>1421</v>
       </c>
-      <c r="B680" s="1" t="s">
-        <v>1422</v>
-      </c>
       <c r="C680" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D680" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E680" s="1" t="s">
         <v>18</v>
@@ -18468,16 +18465,16 @@
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B681" s="1" t="s">
         <v>1423</v>
       </c>
-      <c r="B681" s="1" t="s">
-        <v>1424</v>
-      </c>
       <c r="C681" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D681" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E681" s="1" t="s">
         <v>18</v>
@@ -18488,16 +18485,16 @@
     </row>
     <row r="682" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B682" s="1" t="s">
         <v>1425</v>
       </c>
-      <c r="B682" s="1" t="s">
-        <v>1426</v>
-      </c>
       <c r="C682" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D682" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E682" s="1" t="s">
         <v>21</v>
@@ -18508,16 +18505,16 @@
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B683" s="1" t="s">
         <v>1427</v>
       </c>
-      <c r="B683" s="1" t="s">
-        <v>1428</v>
-      </c>
       <c r="C683" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D683" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E683" s="1" t="s">
         <v>21</v>
@@ -18528,16 +18525,16 @@
     </row>
     <row r="684" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B684" s="1" t="s">
         <v>1429</v>
       </c>
-      <c r="B684" s="1" t="s">
-        <v>1430</v>
-      </c>
       <c r="C684" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D684" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E684" s="1" t="s">
         <v>24</v>
@@ -18548,16 +18545,16 @@
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B685" s="1" t="s">
         <v>1431</v>
       </c>
-      <c r="B685" s="1" t="s">
-        <v>1432</v>
-      </c>
       <c r="C685" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D685" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E685" s="1" t="s">
         <v>24</v>
@@ -18568,16 +18565,16 @@
     </row>
     <row r="686" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B686" s="1" t="s">
         <v>1433</v>
       </c>
-      <c r="B686" s="1" t="s">
-        <v>1434</v>
-      </c>
       <c r="C686" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D686" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E686" s="1" t="s">
         <v>55</v>
@@ -18588,16 +18585,16 @@
     </row>
     <row r="687" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B687" s="1" t="s">
         <v>1435</v>
       </c>
-      <c r="B687" s="1" t="s">
-        <v>1436</v>
-      </c>
       <c r="C687" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D687" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E687" s="1" t="s">
         <v>55</v>
@@ -18608,16 +18605,16 @@
     </row>
     <row r="688" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B688" s="1" t="s">
         <v>1437</v>
       </c>
-      <c r="B688" s="1" t="s">
-        <v>1438</v>
-      </c>
       <c r="C688" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D688" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E688" s="1" t="s">
         <v>28</v>
@@ -18628,16 +18625,16 @@
     </row>
     <row r="689" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B689" s="1" t="s">
         <v>1439</v>
       </c>
-      <c r="B689" s="1" t="s">
-        <v>1440</v>
-      </c>
       <c r="C689" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D689" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E689" s="1" t="s">
         <v>28</v>
@@ -18648,16 +18645,16 @@
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B690" s="1" t="s">
         <v>1441</v>
       </c>
-      <c r="B690" s="1" t="s">
-        <v>1442</v>
-      </c>
       <c r="C690" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D690" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E690" s="1" t="s">
         <v>31</v>
@@ -18668,16 +18665,16 @@
     </row>
     <row r="691" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B691" s="1" t="s">
         <v>1443</v>
       </c>
-      <c r="B691" s="1" t="s">
-        <v>1444</v>
-      </c>
       <c r="C691" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D691" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E691" s="1" t="s">
         <v>31</v>
@@ -18688,16 +18685,16 @@
     </row>
     <row r="692" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B692" s="1" t="s">
         <v>1445</v>
       </c>
-      <c r="B692" s="1" t="s">
-        <v>1446</v>
-      </c>
       <c r="C692" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D692" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E692" s="1" t="s">
         <v>34</v>
@@ -18708,16 +18705,16 @@
     </row>
     <row r="693" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B693" s="1" t="s">
         <v>1447</v>
       </c>
-      <c r="B693" s="1" t="s">
-        <v>1448</v>
-      </c>
       <c r="C693" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D693" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E693" s="1" t="s">
         <v>34</v>
@@ -18728,16 +18725,16 @@
     </row>
     <row r="694" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A694" s="1" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B694" s="1" t="s">
         <v>1449</v>
       </c>
-      <c r="B694" s="1" t="s">
-        <v>1450</v>
-      </c>
       <c r="C694" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D694" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E694" s="1" t="s">
         <v>37</v>
@@ -18748,16 +18745,16 @@
     </row>
     <row r="695" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A695" s="1" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B695" s="1" t="s">
         <v>1451</v>
       </c>
-      <c r="B695" s="1" t="s">
-        <v>1452</v>
-      </c>
       <c r="C695" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D695" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E695" s="1" t="s">
         <v>37</v>
@@ -18768,16 +18765,16 @@
     </row>
     <row r="696" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A696" s="1" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B696" s="1" t="s">
         <v>1453</v>
       </c>
-      <c r="B696" s="1" t="s">
-        <v>1454</v>
-      </c>
       <c r="C696" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D696" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E696" s="1" t="s">
         <v>66</v>
@@ -18788,16 +18785,16 @@
     </row>
     <row r="697" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B697" s="1" t="s">
         <v>1455</v>
       </c>
-      <c r="B697" s="1" t="s">
-        <v>1456</v>
-      </c>
       <c r="C697" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D697" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E697" s="1" t="s">
         <v>66</v>
@@ -18808,16 +18805,16 @@
     </row>
     <row r="698" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A698" s="1" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B698" s="1" t="s">
         <v>1457</v>
       </c>
-      <c r="B698" s="1" t="s">
-        <v>1458</v>
-      </c>
       <c r="C698" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D698" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E698" s="1" t="s">
         <v>98</v>
@@ -18828,16 +18825,16 @@
     </row>
     <row r="699" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A699" s="1" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B699" s="1" t="s">
         <v>1459</v>
       </c>
-      <c r="B699" s="1" t="s">
-        <v>1460</v>
-      </c>
       <c r="C699" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D699" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E699" s="1" t="s">
         <v>101</v>
@@ -18848,16 +18845,16 @@
     </row>
     <row r="700" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A700" s="1" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B700" s="1" t="s">
         <v>1461</v>
       </c>
-      <c r="B700" s="1" t="s">
+      <c r="C700" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D700" s="1" t="s">
         <v>1462</v>
-      </c>
-      <c r="C700" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D700" s="1" t="s">
-        <v>1463</v>
       </c>
       <c r="E700" s="1" t="s">
         <v>15</v>
@@ -18868,16 +18865,16 @@
     </row>
     <row r="701" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A701" s="1" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B701" s="1" t="s">
         <v>1464</v>
       </c>
-      <c r="B701" s="1" t="s">
-        <v>1465</v>
-      </c>
       <c r="C701" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D701" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E701" s="1" t="s">
         <v>18</v>
@@ -18888,16 +18885,16 @@
     </row>
     <row r="702" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A702" s="1" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B702" s="1" t="s">
         <v>1466</v>
       </c>
-      <c r="B702" s="1" t="s">
-        <v>1467</v>
-      </c>
       <c r="C702" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D702" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E702" s="1" t="s">
         <v>21</v>
@@ -18908,16 +18905,16 @@
     </row>
     <row r="703" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A703" s="1" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B703" s="1" t="s">
         <v>1468</v>
       </c>
-      <c r="B703" s="1" t="s">
-        <v>1469</v>
-      </c>
       <c r="C703" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D703" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E703" s="1" t="s">
         <v>24</v>
@@ -18928,16 +18925,16 @@
     </row>
     <row r="704" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A704" s="1" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B704" s="1" t="s">
         <v>1470</v>
       </c>
-      <c r="B704" s="1" t="s">
-        <v>1471</v>
-      </c>
       <c r="C704" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D704" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E704" s="1" t="s">
         <v>55</v>
@@ -18948,16 +18945,16 @@
     </row>
     <row r="705" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A705" s="1" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B705" s="1" t="s">
         <v>1472</v>
       </c>
-      <c r="B705" s="1" t="s">
-        <v>1473</v>
-      </c>
       <c r="C705" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D705" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E705" s="1" t="s">
         <v>28</v>
@@ -18968,16 +18965,16 @@
     </row>
     <row r="706" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A706" s="1" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B706" s="1" t="s">
         <v>1474</v>
       </c>
-      <c r="B706" s="1" t="s">
-        <v>1475</v>
-      </c>
       <c r="C706" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D706" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E706" s="1" t="s">
         <v>31</v>
@@ -18988,16 +18985,16 @@
     </row>
     <row r="707" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A707" s="1" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B707" s="1" t="s">
         <v>1476</v>
       </c>
-      <c r="B707" s="1" t="s">
-        <v>1477</v>
-      </c>
       <c r="C707" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D707" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E707" s="1" t="s">
         <v>34</v>
@@ -19008,16 +19005,16 @@
     </row>
     <row r="708" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A708" s="1" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B708" s="1" t="s">
         <v>1478</v>
       </c>
-      <c r="B708" s="1" t="s">
-        <v>1479</v>
-      </c>
       <c r="C708" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D708" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E708" s="1" t="s">
         <v>37</v>
@@ -19028,16 +19025,16 @@
     </row>
     <row r="709" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A709" s="1" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B709" s="1" t="s">
         <v>1480</v>
       </c>
-      <c r="B709" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="C709" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D709" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E709" s="1" t="s">
         <v>66</v>
@@ -19048,16 +19045,16 @@
     </row>
     <row r="710" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A710" s="1" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B710" s="1" t="s">
         <v>1482</v>
       </c>
-      <c r="B710" s="1" t="s">
-        <v>1483</v>
-      </c>
       <c r="C710" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D710" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E710" s="1" t="s">
         <v>98</v>
